--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e4f0f49ae7a2b34f/Desktop/School Record Mangement System/files/school-record-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_C2057C561633C5B51030240C9ECFEA65B2D385A6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{015F0671-223A-492E-B50F-B04A8853E2BC}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_C2057C561633C5B51030240C9ECFEA65B2D385A6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95E529EB-44EB-479B-829C-8E04FA99FC6B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="225">
   <si>
     <t>Subject Scheduler — Personalized School Record Management System</t>
   </si>
@@ -696,6 +696,12 @@
   </si>
   <si>
     <t>KAByzscj7uPA7NXnDQlHDV6Xww==</t>
+  </si>
+  <si>
+    <t>bc337c10485dc2eb228a89275ad0b2727a824f42d5c8ca14c307e5ead0a73f10</t>
+  </si>
+  <si>
+    <t>zoq27eOgIt/jkkZkdcJB6Q==</t>
   </si>
 </sst>
 </file>
@@ -743,7 +749,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -756,6 +762,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1583,10 +1590,10 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1" s="7"/>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -1700,9 +1707,9 @@
     <col min="1" max="1" width="68" style="2" customWidth="1"/>
     <col min="2" max="2" width="18" style="1" customWidth="1"/>
     <col min="3" max="3" width="30" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14" style="1" customWidth="1"/>
-    <col min="5" max="5" width="26" style="1" customWidth="1"/>
-    <col min="6" max="6" width="68" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="67.125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1740,9 +1747,6 @@
       </c>
       <c r="E2"/>
       <c r="F2"/>
-      <c r="G2">
-        <v>1</v>
-      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -1759,9 +1763,6 @@
       </c>
       <c r="E3"/>
       <c r="F3"/>
-      <c r="G3">
-        <v>2</v>
-      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1778,9 +1779,6 @@
       </c>
       <c r="E4"/>
       <c r="F4"/>
-      <c r="G4">
-        <v>3</v>
-      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -1797,9 +1795,7 @@
       </c>
       <c r="E5"/>
       <c r="F5"/>
-      <c r="G5" s="1">
-        <v>4</v>
-      </c>
+      <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -1816,9 +1812,7 @@
       </c>
       <c r="E6"/>
       <c r="F6"/>
-      <c r="G6" s="1">
-        <v>5</v>
-      </c>
+      <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
@@ -1835,9 +1829,7 @@
       </c>
       <c r="E7"/>
       <c r="F7"/>
-      <c r="G7" s="1">
-        <v>6</v>
-      </c>
+      <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
@@ -1854,9 +1846,7 @@
       </c>
       <c r="E8"/>
       <c r="F8"/>
-      <c r="G8" s="1">
-        <v>7</v>
-      </c>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
@@ -1873,9 +1863,7 @@
       </c>
       <c r="E9"/>
       <c r="F9"/>
-      <c r="G9" s="1">
-        <v>8</v>
-      </c>
+      <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
@@ -1892,9 +1880,7 @@
       </c>
       <c r="E10"/>
       <c r="F10"/>
-      <c r="G10" s="1">
-        <v>9</v>
-      </c>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
@@ -1911,9 +1897,7 @@
       </c>
       <c r="E11"/>
       <c r="F11"/>
-      <c r="G11" s="1">
-        <v>10</v>
-      </c>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
@@ -1930,9 +1914,7 @@
       </c>
       <c r="E12"/>
       <c r="F12"/>
-      <c r="G12" s="1">
-        <v>11</v>
-      </c>
+      <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
@@ -1949,9 +1931,7 @@
       </c>
       <c r="E13"/>
       <c r="F13"/>
-      <c r="G13" s="1">
-        <v>12</v>
-      </c>
+      <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -1968,9 +1948,7 @@
       </c>
       <c r="E14"/>
       <c r="F14"/>
-      <c r="G14" s="1">
-        <v>13</v>
-      </c>
+      <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -1987,9 +1965,7 @@
       </c>
       <c r="E15"/>
       <c r="F15"/>
-      <c r="G15" s="1">
-        <v>14</v>
-      </c>
+      <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
@@ -2006,9 +1982,7 @@
       </c>
       <c r="E16"/>
       <c r="F16"/>
-      <c r="G16" s="1">
-        <v>15</v>
-      </c>
+      <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
@@ -2025,9 +1999,7 @@
       </c>
       <c r="E17"/>
       <c r="F17"/>
-      <c r="G17" s="1">
-        <v>16</v>
-      </c>
+      <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
@@ -2044,9 +2016,7 @@
       </c>
       <c r="E18"/>
       <c r="F18"/>
-      <c r="G18" s="1">
-        <v>17</v>
-      </c>
+      <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
@@ -2063,9 +2033,7 @@
       </c>
       <c r="E19"/>
       <c r="F19"/>
-      <c r="G19" s="1">
-        <v>18</v>
-      </c>
+      <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
@@ -2082,9 +2050,7 @@
       </c>
       <c r="E20"/>
       <c r="F20"/>
-      <c r="G20" s="1">
-        <v>19</v>
-      </c>
+      <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
@@ -2101,9 +2067,7 @@
       </c>
       <c r="E21"/>
       <c r="F21"/>
-      <c r="G21" s="1">
-        <v>20</v>
-      </c>
+      <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
@@ -2124,9 +2088,7 @@
       <c r="F22" t="s">
         <v>156</v>
       </c>
-      <c r="G22" s="1">
-        <v>21</v>
-      </c>
+      <c r="G22" s="1"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
@@ -2143,9 +2105,7 @@
       </c>
       <c r="E23"/>
       <c r="F23"/>
-      <c r="G23" s="1">
-        <v>22</v>
-      </c>
+      <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
@@ -2157,14 +2117,16 @@
       <c r="C24" t="s">
         <v>162</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="E24"/>
-      <c r="F24"/>
-      <c r="G24" s="1">
-        <v>23</v>
-      </c>
+      <c r="E24" t="s">
+        <v>224</v>
+      </c>
+      <c r="F24" t="s">
+        <v>223</v>
+      </c>
+      <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
@@ -2181,9 +2143,7 @@
       </c>
       <c r="E25"/>
       <c r="F25"/>
-      <c r="G25" s="1">
-        <v>24</v>
-      </c>
+      <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
@@ -2200,9 +2160,7 @@
       </c>
       <c r="E26"/>
       <c r="F26"/>
-      <c r="G26" s="1">
-        <v>25</v>
-      </c>
+      <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
@@ -2219,9 +2177,7 @@
       </c>
       <c r="E27"/>
       <c r="F27"/>
-      <c r="G27" s="1">
-        <v>26</v>
-      </c>
+      <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
@@ -2238,9 +2194,7 @@
       </c>
       <c r="E28"/>
       <c r="F28"/>
-      <c r="G28" s="1">
-        <v>27</v>
-      </c>
+      <c r="G28" s="1"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
@@ -2257,9 +2211,7 @@
       </c>
       <c r="E29"/>
       <c r="F29"/>
-      <c r="G29" s="1">
-        <v>28</v>
-      </c>
+      <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
@@ -2276,9 +2228,7 @@
       </c>
       <c r="E30"/>
       <c r="F30"/>
-      <c r="G30" s="1">
-        <v>29</v>
-      </c>
+      <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
@@ -2295,9 +2245,7 @@
       </c>
       <c r="E31"/>
       <c r="F31"/>
-      <c r="G31" s="1">
-        <v>30</v>
-      </c>
+      <c r="G31" s="1"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
@@ -2314,9 +2262,7 @@
       </c>
       <c r="E32"/>
       <c r="F32"/>
-      <c r="G32" s="1">
-        <v>31</v>
-      </c>
+      <c r="G32" s="1"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
@@ -2333,9 +2279,7 @@
       </c>
       <c r="E33"/>
       <c r="F33"/>
-      <c r="G33" s="1">
-        <v>32</v>
-      </c>
+      <c r="G33" s="1"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
@@ -2352,9 +2296,7 @@
       </c>
       <c r="E34"/>
       <c r="F34"/>
-      <c r="G34" s="1">
-        <v>33</v>
-      </c>
+      <c r="G34" s="1"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
@@ -2371,9 +2313,7 @@
       </c>
       <c r="E35"/>
       <c r="F35"/>
-      <c r="G35" s="1">
-        <v>34</v>
-      </c>
+      <c r="G35" s="1"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
@@ -2390,9 +2330,7 @@
       </c>
       <c r="E36"/>
       <c r="F36"/>
-      <c r="G36" s="1">
-        <v>35</v>
-      </c>
+      <c r="G36" s="1"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
@@ -2409,9 +2347,7 @@
       </c>
       <c r="E37"/>
       <c r="F37"/>
-      <c r="G37" s="1">
-        <v>36</v>
-      </c>
+      <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
@@ -2428,9 +2364,7 @@
       </c>
       <c r="E38"/>
       <c r="F38"/>
-      <c r="G38" s="1">
-        <v>37</v>
-      </c>
+      <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
@@ -2447,9 +2381,7 @@
       </c>
       <c r="E39"/>
       <c r="F39"/>
-      <c r="G39" s="1">
-        <v>38</v>
-      </c>
+      <c r="G39" s="1"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
@@ -2466,9 +2398,7 @@
       </c>
       <c r="E40"/>
       <c r="F40"/>
-      <c r="G40" s="1">
-        <v>39</v>
-      </c>
+      <c r="G40" s="1"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
@@ -2485,9 +2415,7 @@
       </c>
       <c r="E41"/>
       <c r="F41"/>
-      <c r="G41" s="1">
-        <v>40</v>
-      </c>
+      <c r="G41" s="1"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
@@ -2504,9 +2432,7 @@
       </c>
       <c r="E42"/>
       <c r="F42"/>
-      <c r="G42" s="1">
-        <v>41</v>
-      </c>
+      <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
@@ -2523,9 +2449,7 @@
       </c>
       <c r="E43"/>
       <c r="F43"/>
-      <c r="G43" s="1">
-        <v>42</v>
-      </c>
+      <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
@@ -2542,9 +2466,7 @@
       </c>
       <c r="E44"/>
       <c r="F44"/>
-      <c r="G44" s="1">
-        <v>43</v>
-      </c>
+      <c r="G44" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e4f0f49ae7a2b34f/Desktop/School Record Mangement System/files/school-record-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_C2057C561633C5B51030240C9ECFEA65B2D385A6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95E529EB-44EB-479B-829C-8E04FA99FC6B}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_C2057C561633C5B51030240C9ECFEA65B2D385A6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BF8F303-869B-4857-A73E-5CEDD1B96C9E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -698,10 +698,10 @@
     <t>KAByzscj7uPA7NXnDQlHDV6Xww==</t>
   </si>
   <si>
-    <t>bc337c10485dc2eb228a89275ad0b2727a824f42d5c8ca14c307e5ead0a73f10</t>
-  </si>
-  <si>
-    <t>zoq27eOgIt/jkkZkdcJB6Q==</t>
+    <t>e950adda7b2a5b132a24dbc607cf908f07f9fe4dfb0133c11a85b8b4edcc69a9</t>
+  </si>
+  <si>
+    <t>Hb2Xf2zApAQZNj2UskAIhQ==</t>
   </si>
 </sst>
 </file>
@@ -2118,14 +2118,10 @@
         <v>162</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E24" t="s">
-        <v>224</v>
-      </c>
-      <c r="F24" t="s">
-        <v>223</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="E24"/>
+      <c r="F24"/>
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2461,11 +2457,15 @@
       <c r="C44" t="s">
         <v>222</v>
       </c>
-      <c r="D44" t="s">
-        <v>93</v>
-      </c>
-      <c r="E44"/>
-      <c r="F44"/>
+      <c r="D44" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E44" t="s">
+        <v>224</v>
+      </c>
+      <c r="F44" t="s">
+        <v>223</v>
+      </c>
       <c r="G44" s="1"/>
     </row>
   </sheetData>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e4f0f49ae7a2b34f/Desktop/School Record Mangement System/files/school-record-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_C2057C561633C5B51030240C9ECFEA65B2D385A6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BF8F303-869B-4857-A73E-5CEDD1B96C9E}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="11_C2057C561633C5B51030240C9ECFEA65B2D385A6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D930D221-93B8-4090-90F8-69EFE767C20F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -512,12 +512,6 @@
     <t>f52bb3ef351b36bc50ec34a92470fb5d84f0e1875af1c5dbdeaf7f0e576f0dab</t>
   </si>
   <si>
-    <t>TRWQYajAfj/KKD3a</t>
-  </si>
-  <si>
-    <t>2RLhGNJu8vQtNPR+6gUxwf4sM1WE</t>
-  </si>
-  <si>
     <t>37de68266788e71bb0de81f05e0c156bf7bab559b360e2f6a9743e85084760f7</t>
   </si>
   <si>
@@ -698,10 +692,16 @@
     <t>KAByzscj7uPA7NXnDQlHDV6Xww==</t>
   </si>
   <si>
-    <t>e950adda7b2a5b132a24dbc607cf908f07f9fe4dfb0133c11a85b8b4edcc69a9</t>
-  </si>
-  <si>
-    <t>Hb2Xf2zApAQZNj2UskAIhQ==</t>
+    <t>Fxw9ylfVktr6t1R2</t>
+  </si>
+  <si>
+    <t>0MUZLvv/XuT7UYKHURIPsAH1+mtc</t>
+  </si>
+  <si>
+    <t>a9/uB5a4J4NKUKw+KKUwWw==</t>
+  </si>
+  <si>
+    <t>8a540e829a20e0c3a02c0abfa5b3de88f3ecb5242347da8bf9f2838b9798eea3</t>
   </si>
 </sst>
 </file>
@@ -2111,28 +2111,32 @@
       <c r="A24" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B24" t="s">
-        <v>161</v>
-      </c>
-      <c r="C24" t="s">
-        <v>162</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="E24"/>
-      <c r="F24"/>
+      <c r="B24" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>224</v>
+      </c>
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B25" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" t="s">
         <v>163</v>
-      </c>
-      <c r="B25" t="s">
-        <v>164</v>
-      </c>
-      <c r="C25" t="s">
-        <v>165</v>
       </c>
       <c r="D25" t="s">
         <v>93</v>
@@ -2143,13 +2147,13 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B26" t="s">
+        <v>165</v>
+      </c>
+      <c r="C26" t="s">
         <v>166</v>
-      </c>
-      <c r="B26" t="s">
-        <v>167</v>
-      </c>
-      <c r="C26" t="s">
-        <v>168</v>
       </c>
       <c r="D26" t="s">
         <v>93</v>
@@ -2160,13 +2164,13 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B27" t="s">
+        <v>168</v>
+      </c>
+      <c r="C27" t="s">
         <v>169</v>
-      </c>
-      <c r="B27" t="s">
-        <v>170</v>
-      </c>
-      <c r="C27" t="s">
-        <v>171</v>
       </c>
       <c r="D27" t="s">
         <v>93</v>
@@ -2177,13 +2181,13 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B28" t="s">
+        <v>171</v>
+      </c>
+      <c r="C28" t="s">
         <v>172</v>
-      </c>
-      <c r="B28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C28" t="s">
-        <v>174</v>
       </c>
       <c r="D28" t="s">
         <v>93</v>
@@ -2194,13 +2198,13 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B29" t="s">
+        <v>174</v>
+      </c>
+      <c r="C29" t="s">
         <v>175</v>
-      </c>
-      <c r="B29" t="s">
-        <v>176</v>
-      </c>
-      <c r="C29" t="s">
-        <v>177</v>
       </c>
       <c r="D29" t="s">
         <v>93</v>
@@ -2211,13 +2215,13 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B30" t="s">
+        <v>177</v>
+      </c>
+      <c r="C30" t="s">
         <v>178</v>
-      </c>
-      <c r="B30" t="s">
-        <v>179</v>
-      </c>
-      <c r="C30" t="s">
-        <v>180</v>
       </c>
       <c r="D30" t="s">
         <v>93</v>
@@ -2228,13 +2232,13 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C31" t="s">
         <v>181</v>
-      </c>
-      <c r="B31" t="s">
-        <v>182</v>
-      </c>
-      <c r="C31" t="s">
-        <v>183</v>
       </c>
       <c r="D31" t="s">
         <v>93</v>
@@ -2245,13 +2249,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B32" t="s">
+        <v>183</v>
+      </c>
+      <c r="C32" t="s">
         <v>184</v>
-      </c>
-      <c r="B32" t="s">
-        <v>185</v>
-      </c>
-      <c r="C32" t="s">
-        <v>186</v>
       </c>
       <c r="D32" t="s">
         <v>93</v>
@@ -2262,13 +2266,13 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B33" t="s">
+        <v>186</v>
+      </c>
+      <c r="C33" t="s">
         <v>187</v>
-      </c>
-      <c r="B33" t="s">
-        <v>188</v>
-      </c>
-      <c r="C33" t="s">
-        <v>189</v>
       </c>
       <c r="D33" t="s">
         <v>93</v>
@@ -2279,13 +2283,13 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B34" t="s">
+        <v>189</v>
+      </c>
+      <c r="C34" t="s">
         <v>190</v>
-      </c>
-      <c r="B34" t="s">
-        <v>191</v>
-      </c>
-      <c r="C34" t="s">
-        <v>192</v>
       </c>
       <c r="D34" t="s">
         <v>93</v>
@@ -2296,13 +2300,13 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B35" t="s">
+        <v>192</v>
+      </c>
+      <c r="C35" t="s">
         <v>193</v>
-      </c>
-      <c r="B35" t="s">
-        <v>194</v>
-      </c>
-      <c r="C35" t="s">
-        <v>195</v>
       </c>
       <c r="D35" t="s">
         <v>93</v>
@@ -2313,13 +2317,13 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B36" t="s">
+        <v>195</v>
+      </c>
+      <c r="C36" t="s">
         <v>196</v>
-      </c>
-      <c r="B36" t="s">
-        <v>197</v>
-      </c>
-      <c r="C36" t="s">
-        <v>198</v>
       </c>
       <c r="D36" t="s">
         <v>93</v>
@@ -2330,13 +2334,13 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B37" t="s">
+        <v>198</v>
+      </c>
+      <c r="C37" t="s">
         <v>199</v>
-      </c>
-      <c r="B37" t="s">
-        <v>200</v>
-      </c>
-      <c r="C37" t="s">
-        <v>201</v>
       </c>
       <c r="D37" t="s">
         <v>93</v>
@@ -2347,13 +2351,13 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B38" t="s">
+        <v>201</v>
+      </c>
+      <c r="C38" t="s">
         <v>202</v>
-      </c>
-      <c r="B38" t="s">
-        <v>203</v>
-      </c>
-      <c r="C38" t="s">
-        <v>204</v>
       </c>
       <c r="D38" t="s">
         <v>93</v>
@@ -2364,13 +2368,13 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B39" t="s">
+        <v>204</v>
+      </c>
+      <c r="C39" t="s">
         <v>205</v>
-      </c>
-      <c r="B39" t="s">
-        <v>206</v>
-      </c>
-      <c r="C39" t="s">
-        <v>207</v>
       </c>
       <c r="D39" t="s">
         <v>93</v>
@@ -2381,13 +2385,13 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B40" t="s">
+        <v>207</v>
+      </c>
+      <c r="C40" t="s">
         <v>208</v>
-      </c>
-      <c r="B40" t="s">
-        <v>209</v>
-      </c>
-      <c r="C40" t="s">
-        <v>210</v>
       </c>
       <c r="D40" t="s">
         <v>93</v>
@@ -2398,13 +2402,13 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B41" t="s">
+        <v>210</v>
+      </c>
+      <c r="C41" t="s">
         <v>211</v>
-      </c>
-      <c r="B41" t="s">
-        <v>212</v>
-      </c>
-      <c r="C41" t="s">
-        <v>213</v>
       </c>
       <c r="D41" t="s">
         <v>93</v>
@@ -2415,13 +2419,13 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B42" t="s">
+        <v>213</v>
+      </c>
+      <c r="C42" t="s">
         <v>214</v>
-      </c>
-      <c r="B42" t="s">
-        <v>215</v>
-      </c>
-      <c r="C42" t="s">
-        <v>216</v>
       </c>
       <c r="D42" t="s">
         <v>93</v>
@@ -2432,13 +2436,13 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B43" t="s">
+        <v>216</v>
+      </c>
+      <c r="C43" t="s">
         <v>217</v>
-      </c>
-      <c r="B43" t="s">
-        <v>218</v>
-      </c>
-      <c r="C43" t="s">
-        <v>219</v>
       </c>
       <c r="D43" t="s">
         <v>93</v>
@@ -2449,23 +2453,19 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B44" t="s">
+        <v>219</v>
+      </c>
+      <c r="C44" t="s">
         <v>220</v>
       </c>
-      <c r="B44" t="s">
-        <v>221</v>
-      </c>
-      <c r="C44" t="s">
-        <v>222</v>
-      </c>
       <c r="D44" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E44" t="s">
-        <v>224</v>
-      </c>
-      <c r="F44" t="s">
-        <v>223</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="E44"/>
+      <c r="F44"/>
       <c r="G44" s="1"/>
     </row>
   </sheetData>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -1634,7 +1634,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -1670,26 +1670,9 @@
         <v>Date</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>ann_1787216314068_o7ngbp</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Test</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Hi</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Bert</v>
-      </c>
-      <c r="E5" t="str">
-        <v>2026-08-20T08:58:34.068Z</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -401,6 +401,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L18"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="30.83203125" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -472,8 +486,20 @@
       <c r="G5" t="str">
         <v>Mon: Online / Fri: Room 307</v>
       </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
       <c r="K5" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -498,8 +524,20 @@
       <c r="G6" t="str">
         <v>Mon: Online / Wed: Room 302</v>
       </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
       <c r="K6" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -527,8 +565,17 @@
       <c r="H7" t="str">
         <v>https://classroom.google.com/u/3/c/ODc0NzY4NDkwNTc0</v>
       </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
       <c r="K7" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -556,8 +603,17 @@
       <c r="H8" t="str">
         <v>https://classroom.google.com/c/ODU1ODc5MTczMjEx</v>
       </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
       <c r="K8" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -585,11 +641,17 @@
       <c r="H9" t="str">
         <v>https://classroom.google.com/c/ODU1ODgxNzY3NTQw?cjc=jl3v4fto</v>
       </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
       <c r="J9" t="str">
         <v>2026-2027</v>
       </c>
       <c r="K9" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -617,11 +679,17 @@
       <c r="H10" t="str">
         <v>https://classroom.google.com/c/ODU1ODgxNzY3NTQw?cjc=jl3v4fto</v>
       </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
       <c r="J10" t="str">
         <v>2026-2027</v>
       </c>
       <c r="K10" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -649,8 +717,17 @@
       <c r="H11" t="str">
         <v>https://classroom.google.com/c/ODU1ODc5MTczMjEx</v>
       </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
       <c r="K11" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -678,8 +755,17 @@
       <c r="H12" t="str">
         <v>https://classroom.google.com/u/3/c/ODc0NzY4NDkwNTc0</v>
       </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
       <c r="K12" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -704,8 +790,20 @@
       <c r="G13" t="str">
         <v>Mon: Online / Wed: Room 302</v>
       </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
       <c r="K13" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -733,11 +831,17 @@
       <c r="H14" t="str">
         <v>https://classroom.google.com/c/ODc0NzQ1NDA2MDEw</v>
       </c>
+      <c r="I14" t="str">
+        <v>https://meet.google.com/landing?authuser=0</v>
+      </c>
       <c r="J14" t="str">
         <v>2026-2027</v>
       </c>
       <c r="K14" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -765,11 +869,17 @@
       <c r="H15" t="str">
         <v>https://classroom.google.com/c/ODc0NzQ1NDA2MDEw</v>
       </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
       <c r="J15" t="str">
         <v>2026-2027</v>
       </c>
       <c r="K15" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -794,8 +904,20 @@
       <c r="G16" t="str">
         <v>Mon: Online / Fri: 307</v>
       </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
       <c r="K16" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -823,11 +945,17 @@
       <c r="H17" t="str">
         <v>https://classroom.google.com/c/ODU1ODc5OTMyNDEz</v>
       </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
       <c r="J17" t="str">
         <v>2026-2027</v>
       </c>
       <c r="K17" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -855,15 +983,20 @@
       <c r="H18" t="str">
         <v>https://classroom.google.com/c/ODU1ODc5NzkxODc0</v>
       </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
       <c r="J18" t="str">
         <v>2026-2027</v>
       </c>
       <c r="K18" t="str">
         <v>1st Sem</v>
       </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
   </ignoredErrors>
@@ -1635,13 +1768,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E4"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -870,7 +870,7 @@
         <v>https://classroom.google.com/c/ODc0NzQ1NDA2MDEw</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>https://meet.google.com/landing?authuser=0</v>
       </c>
       <c r="J15" t="str">
         <v>2026-2027</v>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -604,7 +604,7 @@
         <v>https://classroom.google.com/c/ODU1ODc5MTczMjEx</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>https://meet.google.com/yjs-eqov-wpm?authuser=0</v>
       </c>
       <c r="J8" t="str">
         <v/>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -718,7 +718,7 @@
         <v>https://classroom.google.com/c/ODU1ODc5MTczMjEx</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>https://meet.google.com/yjs-eqov-wpm?authuser=0</v>
       </c>
       <c r="J11" t="str">
         <v/>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -566,7 +566,7 @@
         <v>https://classroom.google.com/u/3/c/ODc0NzY4NDkwNTc0</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>https://meet.google.com/oav-esck-wpt?authuser=0</v>
       </c>
       <c r="J7" t="str">
         <v/>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -756,7 +756,7 @@
         <v>https://classroom.google.com/u/3/c/ODc0NzY4NDkwNTc0</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>https://meet.google.com/oav-esck-wpt?authuser=0</v>
       </c>
       <c r="J12" t="str">
         <v/>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -642,7 +642,7 @@
         <v>https://classroom.google.com/c/ODU1ODgxNzY3NTQw?cjc=jl3v4fto</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>https://meet.google.com/xev-ywxb-toh?authuser=0</v>
       </c>
       <c r="J9" t="str">
         <v>2026-2027</v>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -680,7 +680,7 @@
         <v>https://classroom.google.com/c/ODU1ODgxNzY3NTQw?cjc=jl3v4fto</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>https://meet.google.com/xev-ywxb-toh?authuser=0</v>
       </c>
       <c r="J10" t="str">
         <v>2026-2027</v>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -401,20 +401,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L18"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="24.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" customWidth="1"/>
-    <col min="6" max="6" width="11.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" customWidth="1"/>
-    <col min="12" max="12" width="24.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1767,7 +1753,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="60.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1796,9 +1789,37 @@
         <v>Date</v>
       </c>
     </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>ann_1787217180347_3r0q7r</v>
+      </c>
+      <c r="B5" t="str">
+        <v>IMPORTANT ANNOUNCEMENT!!!</v>
+      </c>
+      <c r="C5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Subject: System Analysis and Design
+Topic: Group Research Project
+Group composition: 1-3
+Deadline of submission of group members: August 22, 2026 - 5:00PM PHT
+Requirements and Guidelines:
+- 5 Research Title per member (5 x No. of member)
+- Allowed:
+1. Web-Based or Application Systems (Desktop/Mobile)
+- Prohibited:
+1. More than 3 members
+2. A.I.-generated shits
+3. Walang bitaw na  member</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2026-08-20T09:13:00.347Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e4f0f49ae7a2b34f/Desktop/School Record Mangement System/files/school-record-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_C2057C561633C5B51030240C9ECFEA65B2D385A6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BF8F303-869B-4857-A73E-5CEDD1B96C9E}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_C2057C561633C5B51030240C9ECFEA65B2D385A6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A58FB794-9B92-4F14-B5EC-B03A8675D30F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="223">
   <si>
     <t>Subject Scheduler — Personalized School Record Management System</t>
   </si>
@@ -696,12 +696,6 @@
   </si>
   <si>
     <t>KAByzscj7uPA7NXnDQlHDV6Xww==</t>
-  </si>
-  <si>
-    <t>e950adda7b2a5b132a24dbc607cf908f07f9fe4dfb0133c11a85b8b4edcc69a9</t>
-  </si>
-  <si>
-    <t>Hb2Xf2zApAQZNj2UskAIhQ==</t>
   </si>
 </sst>
 </file>
@@ -749,7 +743,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -762,6 +756,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -1590,10 +1585,10 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="7"/>
+      <c r="B1" s="8"/>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -2457,15 +2452,11 @@
       <c r="C44" t="s">
         <v>222</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E44" t="s">
-        <v>224</v>
-      </c>
-      <c r="F44" t="s">
-        <v>223</v>
-      </c>
+      <c r="D44" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E44"/>
+      <c r="F44"/>
       <c r="G44" s="1"/>
     </row>
   </sheetData>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -401,6 +401,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L18"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="30.83203125" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -472,8 +486,20 @@
       <c r="G5" t="str">
         <v>Mon: Online / Fri: Room 307</v>
       </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
       <c r="K5" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -498,8 +524,20 @@
       <c r="G6" t="str">
         <v>Mon: Online / Wed: Room 302</v>
       </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
       <c r="K6" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -530,8 +568,14 @@
       <c r="I7" t="str">
         <v>https://meet.google.com/oav-esck-wpt?authuser=0</v>
       </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
       <c r="K7" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -562,8 +606,14 @@
       <c r="I8" t="str">
         <v>https://meet.google.com/yjs-eqov-wpm?authuser=0</v>
       </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
       <c r="K8" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -600,6 +650,9 @@
       <c r="K9" t="str">
         <v>1st Sem</v>
       </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -635,6 +688,9 @@
       <c r="K10" t="str">
         <v>1st Sem</v>
       </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -664,8 +720,14 @@
       <c r="I11" t="str">
         <v>https://meet.google.com/yjs-eqov-wpm?authuser=0</v>
       </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
       <c r="K11" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -696,8 +758,14 @@
       <c r="I12" t="str">
         <v>https://meet.google.com/oav-esck-wpt?authuser=0</v>
       </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
       <c r="K12" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -722,8 +790,20 @@
       <c r="G13" t="str">
         <v>Mon: Online / Wed: Room 302</v>
       </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
       <c r="K13" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -760,6 +840,9 @@
       <c r="K14" t="str">
         <v>1st Sem</v>
       </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -795,6 +878,9 @@
       <c r="K15" t="str">
         <v>1st Sem</v>
       </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -818,8 +904,20 @@
       <c r="G16" t="str">
         <v>Mon: Online / Fri: 307</v>
       </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
       <c r="K16" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -847,11 +945,17 @@
       <c r="H17" t="str">
         <v>https://classroom.google.com/c/ODU1ODc5OTMyNDEz</v>
       </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
       <c r="J17" t="str">
         <v>2026-2027</v>
       </c>
       <c r="K17" t="str">
         <v>1st Sem</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -879,15 +983,20 @@
       <c r="H18" t="str">
         <v>https://classroom.google.com/c/ODU1ODc5NzkxODc0</v>
       </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
       <c r="J18" t="str">
         <v>2026-2027</v>
       </c>
       <c r="K18" t="str">
         <v>1st Sem</v>
       </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
   </ignoredErrors>
@@ -1800,16 +1909,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H5"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -401,20 +401,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L18"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="24.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" customWidth="1"/>
-    <col min="6" max="6" width="11.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" customWidth="1"/>
-    <col min="12" max="12" width="24.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1908,7 +1894,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="60.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1983,9 +1979,36 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>ann_1787222833867_b89eet</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Holiday Tomorrow: NINOY AQUINO DAY</v>
+      </c>
+      <c r="C6" t="str" xml:space="preserve">
+        <v xml:space="preserve">To learn more about this, watch here:
+https://youtu.be/dQw4w9WgXcQ?si=q1vhwdXlbSRL9W-H</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Jerome</v>
+      </c>
+      <c r="E6" t="str">
+        <v>2026-08-20T10:47:13.867Z</v>
+      </c>
+      <c r="F6" t="str">
+        <v>2026-08-20T10:47:13.867Z</v>
+      </c>
+      <c r="G6" t="str">
+        <v>2026-08-20T15:59:59.000Z</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -1964,13 +1964,13 @@
 3. Walang bitaw na  member</v>
       </c>
       <c r="D5" t="str">
-        <v>JC_</v>
+        <v>Bert</v>
       </c>
       <c r="E5" t="str">
         <v>2026-08-20T09:13:00.347Z</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-08-20T10:19:17.322Z</v>
+        <v>2026-08-20T11:27:29.612Z</v>
       </c>
       <c r="G5" t="str">
         <v>2026-08-22T15:59:59.000Z</v>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -1991,16 +1991,16 @@
 https://youtu.be/dQw4w9WgXcQ?si=q1vhwdXlbSRL9W-H</v>
       </c>
       <c r="D6" t="str">
-        <v>Jerome</v>
+        <v>Bert</v>
       </c>
       <c r="E6" t="str">
         <v>2026-08-20T10:47:13.867Z</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-08-20T10:47:13.867Z</v>
+        <v>2026-08-20T17:09:33.670Z</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-08-20T15:59:59.000Z</v>
+        <v>2026-08-21T15:59:59.000Z</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -1984,7 +1984,7 @@
         <v>ann_1787222833867_b89eet</v>
       </c>
       <c r="B6" t="str">
-        <v>Holiday Tomorrow: NINOY AQUINO DAY</v>
+        <v>Holiday: August 21, 2026 PH - NINOY AQUINO DAY</v>
       </c>
       <c r="C6" t="str" xml:space="preserve">
         <v xml:space="preserve">To learn more about this, watch here:
@@ -1997,7 +1997,7 @@
         <v>2026-08-20T10:47:13.867Z</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-08-20T17:09:33.670Z</v>
+        <v>2026-08-20T17:10:18.646Z</v>
       </c>
       <c r="G6" t="str">
         <v>2026-08-21T15:59:59.000Z</v>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -1947,7 +1947,7 @@
         <v>ann_1787217180347_3r0q7r</v>
       </c>
       <c r="B5" t="str">
-        <v>IMPORTANT ANNOUNCEMENT!!!</v>
+        <v>Update: System Analysis and Design</v>
       </c>
       <c r="C5" t="str" xml:space="preserve">
         <v xml:space="preserve">Subject: System Analysis and Design
@@ -1970,7 +1970,7 @@
         <v>2026-08-20T09:13:00.347Z</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-08-20T11:27:29.612Z</v>
+        <v>2026-08-20T17:10:56.251Z</v>
       </c>
       <c r="G5" t="str">
         <v>2026-08-22T15:59:59.000Z</v>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -1894,7 +1894,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -1979,36 +1979,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" xml:space="preserve">
-      <c r="A6" t="str">
-        <v>ann_1787222833867_b89eet</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Holiday: August 21, 2026 PH - NINOY AQUINO DAY</v>
-      </c>
-      <c r="C6" t="str" xml:space="preserve">
-        <v xml:space="preserve">To learn more about this, watch here:
-https://youtu.be/dQw4w9WgXcQ?si=q1vhwdXlbSRL9W-H</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Bert</v>
-      </c>
-      <c r="E6" t="str">
-        <v>2026-08-20T10:47:13.867Z</v>
-      </c>
-      <c r="F6" t="str">
-        <v>2026-08-20T17:10:18.646Z</v>
-      </c>
-      <c r="G6" t="str">
-        <v>2026-08-21T15:59:59.000Z</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -7,6 +7,8 @@
     <sheet name="Legend" sheetId="2" r:id="rId2"/>
     <sheet name="Valid_Users" sheetId="3" r:id="rId3"/>
     <sheet name="Announcements" sheetId="4" r:id="rId4"/>
+    <sheet name="Flashcards" sheetId="5" r:id="rId5"/>
+    <sheet name="Audit_Log" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -1895,16 +1897,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H5"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1984,4 +1976,166 @@
     <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H5"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="5" max="5" width="40.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Flashcards — Personalized School Record Management System</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Master accounts add/edit/delete cards here; anyone signed in can review them.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Deck</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Type</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Front</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Back</v>
+      </c>
+      <c r="F4" t="str">
+        <v>CreatedBy</v>
+      </c>
+      <c r="G4" t="str">
+        <v>CreatedAt</v>
+      </c>
+      <c r="H4" t="str">
+        <v>UpdatedAt</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>card_1787420985723_5bswth</v>
+      </c>
+      <c r="B5" t="str">
+        <v>DM101-Plannin</v>
+      </c>
+      <c r="C5" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Front Test</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Back Test</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G5" t="str">
+        <v>2026-08-22T17:49:45.723Z</v>
+      </c>
+      <c r="H5" t="str">
+        <v>2026-08-22T17:49:45.723Z</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E6"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="42.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Audit Log — Personalized School Record Management System</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Read-only history of sign-ins and changes. Visible to Master accounts only, and not editable through any app UI.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Timestamp</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Actor</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Role</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Action</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Details</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-08-23T01:48:01+08:00</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Login</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Master</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2026-08-23T01:49:45+08:00</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E6" t="str">
+        <v>DM101-Plannin</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -1980,7 +1980,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -2054,16 +2054,42 @@
         <v>2026-08-22T17:49:45.723Z</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>card_1787421039976_2qwhp5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>DM101-Planning</v>
+      </c>
+      <c r="C6" t="str">
+        <v>cloze</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Hello there _____.</v>
+      </c>
+      <c r="E6" t="str">
+        <v>My friend</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G6" t="str">
+        <v>2026-08-22T17:50:39.976Z</v>
+      </c>
+      <c r="H6" t="str">
+        <v>2026-08-22T17:50:39.976Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -2133,9 +2159,26 @@
         <v>DM101-Plannin</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2026-08-23T01:50:39+08:00</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E7" t="str">
+        <v>DM101-Planning — cloze</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -1980,7 +1980,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -2030,66 +2030,40 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>card_1787420985723_5bswth</v>
+        <v>card_1787421039976_2qwhp5</v>
       </c>
       <c r="B5" t="str">
-        <v>DM101-Plannin</v>
+        <v>DM101-Planning</v>
       </c>
       <c r="C5" t="str">
-        <v>basic</v>
+        <v>cloze</v>
       </c>
       <c r="D5" t="str">
-        <v>Front Test</v>
+        <v>Hello there _____.</v>
       </c>
       <c r="E5" t="str">
-        <v>Back Test</v>
+        <v>My friend</v>
       </c>
       <c r="F5" t="str">
         <v>Bert</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-08-22T17:49:45.723Z</v>
+        <v>2026-08-22T17:50:39.976Z</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-08-22T17:49:45.723Z</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>card_1787421039976_2qwhp5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>DM101-Planning</v>
-      </c>
-      <c r="C6" t="str">
-        <v>cloze</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Hello there _____.</v>
-      </c>
-      <c r="E6" t="str">
-        <v>My friend</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Bert</v>
-      </c>
-      <c r="G6" t="str">
-        <v>2026-08-22T17:50:39.976Z</v>
-      </c>
-      <c r="H6" t="str">
         <v>2026-08-22T17:50:39.976Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -2176,9 +2150,43 @@
         <v>DM101-Planning — cloze</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2026-08-23T01:51:12+08:00</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Login</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Master</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-08-23T01:51:46+08:00</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Delete Flashcard</v>
+      </c>
+      <c r="E9" t="str">
+        <v>DM101-Plannin — Front Test</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -1980,7 +1980,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H4"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -2028,42 +2028,16 @@
         <v>UpdatedAt</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>card_1787421039976_2qwhp5</v>
-      </c>
-      <c r="B5" t="str">
-        <v>DM101-Planning</v>
-      </c>
-      <c r="C5" t="str">
-        <v>cloze</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Hello there _____.</v>
-      </c>
-      <c r="E5" t="str">
-        <v>My friend</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Bert</v>
-      </c>
-      <c r="G5" t="str">
-        <v>2026-08-22T17:50:39.976Z</v>
-      </c>
-      <c r="H5" t="str">
-        <v>2026-08-22T17:50:39.976Z</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -2184,9 +2158,43 @@
         <v>DM101-Plannin — Front Test</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-08-23T01:52:26+08:00</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Login</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Master</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026-08-23T01:52:41+08:00</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Delete Flashcard</v>
+      </c>
+      <c r="E11" t="str">
+        <v>DM101-Planning — Hello there _____.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -1896,7 +1896,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H4"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="60.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1934,46 +1944,9 @@
         <v>Pinned</v>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
-      <c r="A5" t="str">
-        <v>ann_1787217180347_3r0q7r</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Update: System Analysis and Design</v>
-      </c>
-      <c r="C5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: System Analysis and Design
-Topic: Group Research Project
-Group composition: 1-3
-Deadline of submission of group members: August 22, 2026 - 5:00PM PHT
-Requirements and Guidelines:
-- 5 Research Title per member (5 x No. of member)
-- Allowed:
-1. Web-Based or Application Systems (Desktop/Mobile)
-- Prohibited:
-1. More than 3 members
-2. A.I.-generated shits
-3. Walang bitaw na  member</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Bert</v>
-      </c>
-      <c r="E5" t="str">
-        <v>2026-08-20T09:13:00.347Z</v>
-      </c>
-      <c r="F5" t="str">
-        <v>2026-08-20T17:10:56.251Z</v>
-      </c>
-      <c r="G5" t="str">
-        <v>2026-08-22T15:59:59.000Z</v>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1981,16 +1954,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H4"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
-    <col min="5" max="5" width="40.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2037,7 +2000,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -2192,9 +2155,43 @@
         <v>DM101-Planning — Hello there _____.</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-08-23T01:53:16+08:00</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Login</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Master</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-08-23T01:53:21+08:00</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Delete Announcement</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Update: System Analysis and Design</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -1896,7 +1896,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -1944,9 +1944,35 @@
         <v>Pinned</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ann_1787421548723_uui0z2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Reminder</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Drink water daily ❤️</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2026-08-22T17:59:08.723Z</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2026-08-22T17:59:08.723Z</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2000,7 +2026,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -2189,9 +2215,43 @@
         <v>Update: System Analysis and Design</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026-08-23T01:56:26+08:00</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Login</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Master</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-08-23T01:59:08+08:00</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Add Announcement</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Reminder</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -490,7 +490,7 @@
         <v>Mon: Online / Fri: Room 307</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>https://classroom.google.com/c/ODc0NzI1NDEzMjYw/m/ODc1NTY5NDgxOTMy/details</v>
       </c>
       <c r="I5" t="str">
         <v>https://meet.google.com/uue-itbf-scf</v>
@@ -4879,7 +4879,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E187"/>
+  <dimension ref="A1:E188"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8026,9 +8026,26 @@
         <v>MAT110 — Quantitative Methods</v>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>2026-09-05T20:06:34+08:00</v>
+      </c>
+      <c r="B188" t="str">
+        <v>test_dummy</v>
+      </c>
+      <c r="C188" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D188" t="str">
+        <v>Edit Subject</v>
+      </c>
+      <c r="E188" t="str">
+        <v>DM103 — Business Process Design and Management</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E187"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E188"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -908,7 +908,7 @@
         <v>Mon: Online / Fri: 307</v>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>https://classroom.google.com/c/ODc0NzI1NDEzMjYw/m/ODc1NTY5NDgxOTMy/details</v>
       </c>
       <c r="I16" t="str">
         <v>https://meet.google.com/uue-itbf-scf</v>
@@ -4879,7 +4879,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E188"/>
+  <dimension ref="A1:E189"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8043,9 +8043,26 @@
         <v>DM103 — Business Process Design and Management</v>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>2026-09-05T20:06:45+08:00</v>
+      </c>
+      <c r="B189" t="str">
+        <v>test_dummy</v>
+      </c>
+      <c r="C189" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D189" t="str">
+        <v>Edit Subject</v>
+      </c>
+      <c r="E189" t="str">
+        <v>DM103 — Business Process Design and Management</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E188"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E189"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -908,7 +908,7 @@
         <v>Mon: Online / Fri: 307</v>
       </c>
       <c r="H16" t="str">
-        <v>https://classroom.google.com/c/ODc0NzI1NDEzMjYw/m/ODc1NTY5NDgxOTMy/details</v>
+        <v>https://classroom.google.com/c/ODc0NzI1NDEzMjYw</v>
       </c>
       <c r="I16" t="str">
         <v>https://meet.google.com/uue-itbf-scf</v>
@@ -4879,7 +4879,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E189"/>
+  <dimension ref="A1:E190"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8060,9 +8060,26 @@
         <v>DM103 — Business Process Design and Management</v>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>2026-09-05T20:07:05+08:00</v>
+      </c>
+      <c r="B190" t="str">
+        <v>test_dummy</v>
+      </c>
+      <c r="C190" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D190" t="str">
+        <v>Edit Subject</v>
+      </c>
+      <c r="E190" t="str">
+        <v>DM103 — Business Process Design and Management</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E189"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E190"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -490,7 +490,7 @@
         <v>Mon: Online / Fri: Room 307</v>
       </c>
       <c r="H5" t="str">
-        <v>https://classroom.google.com/c/ODc0NzI1NDEzMjYw/m/ODc1NTY5NDgxOTMy/details</v>
+        <v>https://classroom.google.com/c/ODc0NzI1NDEzMjYw</v>
       </c>
       <c r="I5" t="str">
         <v>https://meet.google.com/uue-itbf-scf</v>
@@ -4879,7 +4879,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E190"/>
+  <dimension ref="A1:E191"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8077,9 +8077,26 @@
         <v>DM103 — Business Process Design and Management</v>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>2026-09-05T20:07:13+08:00</v>
+      </c>
+      <c r="B191" t="str">
+        <v>test_dummy</v>
+      </c>
+      <c r="C191" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D191" t="str">
+        <v>Edit Subject</v>
+      </c>
+      <c r="E191" t="str">
+        <v>DM103 — Business Process Design and Management</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E190"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E191"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -4879,7 +4879,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E191"/>
+  <dimension ref="A1:E192"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8094,9 +8094,26 @@
         <v>DM103 — Business Process Design and Management</v>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>2026-09-05T20:07:23+08:00</v>
+      </c>
+      <c r="B192" t="str">
+        <v>test_dummy</v>
+      </c>
+      <c r="C192" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D192" t="str">
+        <v>Edit Subject</v>
+      </c>
+      <c r="E192" t="str">
+        <v>MAT110 — Quantitative Methods</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E191"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E192"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -794,7 +794,7 @@
         <v>Mon: Online / Wed: Room 302</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>https://classroom.google.com/u/0/c/ODY5MTQ0MjY2NTA2</v>
       </c>
       <c r="I13" t="str">
         <v>https://meet.google.com/dva-toai-vjo</v>
@@ -4879,7 +4879,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E192"/>
+  <dimension ref="A1:E193"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8111,9 +8111,26 @@
         <v>MAT110 — Quantitative Methods</v>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>2026-09-05T20:07:38+08:00</v>
+      </c>
+      <c r="B193" t="str">
+        <v>test_dummy</v>
+      </c>
+      <c r="C193" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D193" t="str">
+        <v>Edit Subject</v>
+      </c>
+      <c r="E193" t="str">
+        <v>MAT110 — Quantitative Methods</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E192"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E193"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -404,20 +404,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L18"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="24.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" customWidth="1"/>
-    <col min="6" max="6" width="11.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" customWidth="1"/>
-    <col min="12" max="12" width="24.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2153,7 +2139,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H108"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="5" max="5" width="40.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4869,17 +4865,43 @@
         <v>2026-08-29T18:15:52.396Z</v>
       </c>
     </row>
+    <row r="108" xml:space="preserve">
+      <c r="A108" t="str">
+        <v>card_1788688176189_x0znxp</v>
+      </c>
+      <c r="B108" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+      <c r="C108" t="str">
+        <v>cloze</v>
+      </c>
+      <c r="D108" t="str" xml:space="preserve">
+        <v xml:space="preserve">_____ is a systematic record of facts, such as numbers, words, measurements, observations or just
+descriptions of things from which conclusions may be drawn.</v>
+      </c>
+      <c r="E108" t="str">
+        <v>Data</v>
+      </c>
+      <c r="F108" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G108" t="str">
+        <v>2026-09-06T09:49:36.189Z</v>
+      </c>
+      <c r="H108" t="str">
+        <v>2026-09-06T09:49:36.189Z</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H107"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E196"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8128,9 +8150,60 @@
         <v>MAT110 — Quantitative Methods</v>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>2026-09-06T17:46:40+08:00</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C194" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D194" t="str">
+        <v>Login</v>
+      </c>
+      <c r="E194" t="str">
+        <v>Master</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>2026-09-06T17:46:51+08:00</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C195" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D195" t="str">
+        <v>Login</v>
+      </c>
+      <c r="E195" t="str">
+        <v>Master</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>2026-09-06T17:49:36+08:00</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C196" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D196" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E196" t="str">
+        <v>MAT110 - Lesson1 — cloze</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E193"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E196"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -4865,7 +4865,7 @@
         <v>2026-08-29T18:15:52.396Z</v>
       </c>
     </row>
-    <row r="108" xml:space="preserve">
+    <row r="108">
       <c r="A108" t="str">
         <v>card_1788688176189_x0znxp</v>
       </c>
@@ -4875,9 +4875,8 @@
       <c r="C108" t="str">
         <v>cloze</v>
       </c>
-      <c r="D108" t="str" xml:space="preserve">
-        <v xml:space="preserve">_____ is a systematic record of facts, such as numbers, words, measurements, observations or just
-descriptions of things from which conclusions may be drawn.</v>
+      <c r="D108" t="str">
+        <v>_____ is a systematic record of facts, such as numbers, words, measurements, observations or just descriptions of things from which conclusions may be drawn.</v>
       </c>
       <c r="E108" t="str">
         <v>Data</v>
@@ -4889,7 +4888,7 @@
         <v>2026-09-06T09:49:36.189Z</v>
       </c>
       <c r="H108" t="str">
-        <v>2026-09-06T09:49:36.189Z</v>
+        <v>2026-09-06T09:49:53.083Z</v>
       </c>
     </row>
   </sheetData>
@@ -4901,7 +4900,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E196"/>
+  <dimension ref="A1:E197"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8201,9 +8200,26 @@
         <v>MAT110 - Lesson1 — cloze</v>
       </c>
     </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>2026-09-06T17:49:53+08:00</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C197" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D197" t="str">
+        <v>Edit Flashcard</v>
+      </c>
+      <c r="E197" t="str">
+        <v>MAT110 - Lesson1 — cloze</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E196"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E197"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H109"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -4891,16 +4891,43 @@
         <v>2026-09-06T09:49:53.083Z</v>
       </c>
     </row>
+    <row r="109" xml:space="preserve">
+      <c r="A109" t="str">
+        <v>card_1788688229601_t8juvp</v>
+      </c>
+      <c r="B109" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+      <c r="C109" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Types of Data</v>
+      </c>
+      <c r="E109" t="str" xml:space="preserve">
+        <v xml:space="preserve">- Qualitative data
+- Quantitative data</v>
+      </c>
+      <c r="F109" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G109" t="str">
+        <v>2026-09-06T09:50:29.601Z</v>
+      </c>
+      <c r="H109" t="str">
+        <v>2026-09-06T09:50:29.601Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H109"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E197"/>
+  <dimension ref="A1:E198"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8217,9 +8244,26 @@
         <v>MAT110 - Lesson1 — cloze</v>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>2026-09-06T17:50:29+08:00</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C198" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D198" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E198" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E197"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E198"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H110"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -4918,16 +4918,42 @@
         <v>2026-09-06T09:50:29.601Z</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>card_1788688260176_zsl7ob</v>
+      </c>
+      <c r="B110" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+      <c r="C110" t="str">
+        <v>cloze</v>
+      </c>
+      <c r="D110" t="str">
+        <v>_____ is data that is not given numerically. Data are measures of "types" and may be represented by a name, symbol, or a number code.</v>
+      </c>
+      <c r="E110" t="str">
+        <v>Qualitative data</v>
+      </c>
+      <c r="F110" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G110" t="str">
+        <v>2026-09-06T09:51:00.176Z</v>
+      </c>
+      <c r="H110" t="str">
+        <v>2026-09-06T09:51:00.176Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H109"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H110"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E198"/>
+  <dimension ref="A1:E199"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8261,9 +8287,26 @@
         <v>MAT110 - Lesson1</v>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>2026-09-06T17:51:00+08:00</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C199" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D199" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E199" t="str">
+        <v>MAT110 - Lesson1 — cloze</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E198"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E199"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:H111"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -4944,16 +4944,42 @@
         <v>2026-09-06T09:51:00.176Z</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>card_1788688298974_hj7az0</v>
+      </c>
+      <c r="B111" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+      <c r="C111" t="str">
+        <v>cloze</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Qualitative data is data that is not given numerically. Data are measures of _____ and may be represented by a name, symbol, or a number code.</v>
+      </c>
+      <c r="E111" t="str">
+        <v>'types'</v>
+      </c>
+      <c r="F111" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G111" t="str">
+        <v>2026-09-06T09:51:38.974Z</v>
+      </c>
+      <c r="H111" t="str">
+        <v>2026-09-06T09:51:38.974Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H110"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H111"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E199"/>
+  <dimension ref="A1:E200"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8304,9 +8330,26 @@
         <v>MAT110 - Lesson1 — cloze</v>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>2026-09-06T17:51:38+08:00</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C200" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D200" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E200" t="str">
+        <v>MAT110 - Lesson1 — cloze</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E200"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H111"/>
+  <dimension ref="A1:H112"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -4970,16 +4970,42 @@
         <v>2026-09-06T09:51:38.974Z</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>card_1788688336276_xbjl52</v>
+      </c>
+      <c r="B112" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+      <c r="C112" t="str">
+        <v>cloze</v>
+      </c>
+      <c r="D112" t="str">
+        <v>_____ is numerical. Data are measures of values or counts and are expressed as numbers.</v>
+      </c>
+      <c r="E112" t="str">
+        <v>Quantitative data</v>
+      </c>
+      <c r="F112" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G112" t="str">
+        <v>2026-09-06T09:52:16.276Z</v>
+      </c>
+      <c r="H112" t="str">
+        <v>2026-09-06T09:52:16.276Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H111"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H112"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E200"/>
+  <dimension ref="A1:E201"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8347,9 +8373,26 @@
         <v>MAT110 - Lesson1 — cloze</v>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>2026-09-06T17:52:16+08:00</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C201" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D201" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E201" t="str">
+        <v>MAT110 - Lesson1 — cloze</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E201"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H112"/>
+  <dimension ref="A1:H113"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -4996,16 +4996,43 @@
         <v>2026-09-06T09:52:16.276Z</v>
       </c>
     </row>
+    <row r="113" xml:space="preserve">
+      <c r="A113" t="str">
+        <v>card_1788688376585_2c2v37</v>
+      </c>
+      <c r="B113" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+      <c r="C113" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D113" t="str">
+        <v>2 Types of Quantitative Data</v>
+      </c>
+      <c r="E113" t="str" xml:space="preserve">
+        <v xml:space="preserve">- Discrete data
+- Continuous data</v>
+      </c>
+      <c r="F113" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G113" t="str">
+        <v>2026-09-06T09:52:56.585Z</v>
+      </c>
+      <c r="H113" t="str">
+        <v>2026-09-06T09:52:56.585Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H112"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H113"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E201"/>
+  <dimension ref="A1:E202"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8390,9 +8417,26 @@
         <v>MAT110 - Lesson1 — cloze</v>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>2026-09-06T17:52:56+08:00</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C202" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D202" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E202" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E201"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E202"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:H114"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5023,16 +5023,43 @@
         <v>2026-09-06T09:52:56.585Z</v>
       </c>
     </row>
+    <row r="114" xml:space="preserve">
+      <c r="A114" t="str">
+        <v>card_1788688427495_h6kp8c</v>
+      </c>
+      <c r="B114" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+      <c r="C114" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Type of data that can only take specific numeric values.</v>
+      </c>
+      <c r="E114" t="str" xml:space="preserve">
+        <v xml:space="preserve">Discrete
+Examples: shoe size, number of brothers, number of cars in a car park</v>
+      </c>
+      <c r="F114" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G114" t="str">
+        <v>2026-09-06T09:53:47.495Z</v>
+      </c>
+      <c r="H114" t="str">
+        <v>2026-09-06T09:53:47.495Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H113"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H114"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E202"/>
+  <dimension ref="A1:E203"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8434,9 +8461,26 @@
         <v>MAT110 - Lesson1</v>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>2026-09-06T17:53:47+08:00</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C203" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D203" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E203" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E202"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E203"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H115"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5050,16 +5050,43 @@
         <v>2026-09-06T09:53:47.495Z</v>
       </c>
     </row>
+    <row r="115" xml:space="preserve">
+      <c r="A115" t="str">
+        <v>card_1788688478916_h3h816</v>
+      </c>
+      <c r="B115" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+      <c r="C115" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Type of data that can take any numerical value; data have infinite possibilities.</v>
+      </c>
+      <c r="E115" t="str" xml:space="preserve">
+        <v xml:space="preserve">Continuous data
+Examples: height, mass, length</v>
+      </c>
+      <c r="F115" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G115" t="str">
+        <v>2026-09-06T09:54:38.916Z</v>
+      </c>
+      <c r="H115" t="str">
+        <v>2026-09-06T09:54:38.916Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H114"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H115"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E203"/>
+  <dimension ref="A1:E204"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8478,9 +8505,26 @@
         <v>MAT110 - Lesson1</v>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>2026-09-06T17:54:38+08:00</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C204" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D204" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E204" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E203"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E204"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -5037,7 +5037,7 @@
         <v>Type of data that can only take specific numeric values.</v>
       </c>
       <c r="E114" t="str" xml:space="preserve">
-        <v xml:space="preserve">Discrete
+        <v xml:space="preserve">Discrete data
 Examples: shoe size, number of brothers, number of cars in a car park</v>
       </c>
       <c r="F114" t="str">
@@ -5047,7 +5047,7 @@
         <v>2026-09-06T09:53:47.495Z</v>
       </c>
       <c r="H114" t="str">
-        <v>2026-09-06T09:53:47.495Z</v>
+        <v>2026-09-06T09:54:45.643Z</v>
       </c>
     </row>
     <row r="115" xml:space="preserve">
@@ -5086,7 +5086,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E204"/>
+  <dimension ref="A1:E205"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8522,9 +8522,26 @@
         <v>MAT110 - Lesson1</v>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>2026-09-06T17:54:45+08:00</v>
+      </c>
+      <c r="B205" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C205" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D205" t="str">
+        <v>Edit Flashcard</v>
+      </c>
+      <c r="E205" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E204"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E205"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H116"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5077,16 +5077,42 @@
         <v>2026-09-06T09:54:38.916Z</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>card_1788688558231_punhmj</v>
+      </c>
+      <c r="B116" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+      <c r="C116" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Example of Primary source</v>
+      </c>
+      <c r="E116" t="str">
+        <v>Novel, Painting, Letters and diaries written by a historical figure, Essay by a philosopher, Photographs of a historical event, Government documents about a new policy, Music recordings, Results of an opinion poll. Empirical study</v>
+      </c>
+      <c r="F116" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G116" t="str">
+        <v>2026-09-06T09:55:58.231Z</v>
+      </c>
+      <c r="H116" t="str">
+        <v>2026-09-06T09:55:58.231Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H115"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H116"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E205"/>
+  <dimension ref="A1:E206"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8539,9 +8565,26 @@
         <v>MAT110 - Lesson1</v>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>2026-09-06T17:55:58+08:00</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C206" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D206" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E206" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E205"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E206"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H117"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5103,16 +5103,43 @@
         <v>2026-09-06T09:55:58.231Z</v>
       </c>
     </row>
+    <row r="117" xml:space="preserve">
+      <c r="A117" t="str">
+        <v>card_1788688647987_tu6wzh</v>
+      </c>
+      <c r="B117" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+      <c r="C117" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Example of Secondary Source</v>
+      </c>
+      <c r="E117" t="str" xml:space="preserve">
+        <v xml:space="preserve">Article analyzing the novel
+Exhibition catalog explaining the painting, Biography of the historical figure, Textbook summarizing the philosopher's ideas, Documentary about the historical event, Newspaper article about the new policy, Academic book about the musical style, Blog post interpreting the results of the poll, Literature review that cites the study</v>
+      </c>
+      <c r="F117" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G117" t="str">
+        <v>2026-09-06T09:57:27.987Z</v>
+      </c>
+      <c r="H117" t="str">
+        <v>2026-09-06T09:57:27.987Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H116"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H117"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E206"/>
+  <dimension ref="A1:E207"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8582,9 +8609,26 @@
         <v>MAT110 - Lesson1</v>
       </c>
     </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>2026-09-06T17:57:27+08:00</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C207" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D207" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E207" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E206"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E207"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H118"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5130,16 +5130,47 @@
         <v>2026-09-06T09:57:27.987Z</v>
       </c>
     </row>
+    <row r="118" xml:space="preserve">
+      <c r="A118" t="str">
+        <v>card_1788688719031_2c86qa</v>
+      </c>
+      <c r="B118" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+      <c r="C118" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D118" t="str">
+        <v>6 Data Collection Methods</v>
+      </c>
+      <c r="E118" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Interviews
+2. Observation
+3. Documents and records
+4. Focus groups
+5. Questionnaires and surveys
+6. Experimentation</v>
+      </c>
+      <c r="F118" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G118" t="str">
+        <v>2026-09-06T09:58:39.031Z</v>
+      </c>
+      <c r="H118" t="str">
+        <v>2026-09-06T09:58:39.031Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H117"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H118"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E207"/>
+  <dimension ref="A1:E208"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8626,9 +8657,26 @@
         <v>MAT110 - Lesson1</v>
       </c>
     </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>2026-09-06T17:58:39+08:00</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C208" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D208" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E208" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E207"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E208"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:H119"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5161,16 +5161,42 @@
         <v>2026-09-06T09:58:39.031Z</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>card_1788688800866_6yuuxg</v>
+      </c>
+      <c r="B119" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+      <c r="C119" t="str">
+        <v>cloze</v>
+      </c>
+      <c r="D119" t="str">
+        <v>_____ are used to collect data from a small group of subjects on a broad range of topics.</v>
+      </c>
+      <c r="E119" t="str">
+        <v>Interviews</v>
+      </c>
+      <c r="F119" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G119" t="str">
+        <v>2026-09-06T10:00:00.866Z</v>
+      </c>
+      <c r="H119" t="str">
+        <v>2026-09-06T10:00:00.866Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H118"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H119"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E208"/>
+  <dimension ref="A1:E209"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8674,9 +8700,26 @@
         <v>MAT110 - Lesson1</v>
       </c>
     </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>2026-09-06T18:00:00+08:00</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C209" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D209" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E209" t="str">
+        <v>MAT110 - Lesson1 — cloze</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E208"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E209"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H119"/>
+  <dimension ref="A1:H120"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5187,16 +5187,42 @@
         <v>2026-09-06T10:00:00.866Z</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>card_1788688851847_6vv54u</v>
+      </c>
+      <c r="B120" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+      <c r="C120" t="str">
+        <v>cloze</v>
+      </c>
+      <c r="D120" t="str">
+        <v>_____ involves collecting information without asking questions. This method is more subjective, as it requires the researcher, or observer, to add their judgment to the data.</v>
+      </c>
+      <c r="E120" t="str">
+        <v>Observation</v>
+      </c>
+      <c r="F120" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G120" t="str">
+        <v>2026-09-06T10:00:51.847Z</v>
+      </c>
+      <c r="H120" t="str">
+        <v>2026-09-06T10:00:51.847Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H119"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H120"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E209"/>
+  <dimension ref="A1:E210"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8717,9 +8743,26 @@
         <v>MAT110 - Lesson1 — cloze</v>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>2026-09-06T18:00:51+08:00</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C210" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D210" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E210" t="str">
+        <v>MAT110 - Lesson1 — cloze</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E209"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E210"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H120"/>
+  <dimension ref="A1:H121"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5213,16 +5213,42 @@
         <v>2026-09-06T10:00:51.847Z</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>card_1788689079251_s8etpw</v>
+      </c>
+      <c r="B121" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+      <c r="C121" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D121" t="str">
+        <v>It is a type of research that uses existing data for a study. Attendance records, meeting minutes, and financial records are just a few examples of this type of research.</v>
+      </c>
+      <c r="E121" t="str">
+        <v>Documents and records</v>
+      </c>
+      <c r="F121" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G121" t="str">
+        <v>2026-09-06T10:04:39.251Z</v>
+      </c>
+      <c r="H121" t="str">
+        <v>2026-09-06T10:04:39.251Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H120"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H121"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E210"/>
+  <dimension ref="A1:E211"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8760,9 +8786,26 @@
         <v>MAT110 - Lesson1 — cloze</v>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>2026-09-06T18:04:39+08:00</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D211" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E211" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E210"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E211"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H122"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5239,16 +5239,42 @@
         <v>2026-09-06T10:04:39.251Z</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>card_1788689137528_wy9rr7</v>
+      </c>
+      <c r="B122" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+      <c r="C122" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D122" t="str">
+        <v>It is a data collection method that involves several individuals who have something in common.</v>
+      </c>
+      <c r="E122" t="str">
+        <v>Focus groups</v>
+      </c>
+      <c r="F122" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G122" t="str">
+        <v>2026-09-06T10:05:37.528Z</v>
+      </c>
+      <c r="H122" t="str">
+        <v>2026-09-06T10:05:37.528Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H121"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H122"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E211"/>
+  <dimension ref="A1:E212"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8803,9 +8829,26 @@
         <v>MAT110 - Lesson1</v>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>2026-09-06T18:05:37+08:00</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C212" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D212" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E212" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E211"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E212"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H122"/>
+  <dimension ref="A1:H123"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5265,16 +5265,42 @@
         <v>2026-09-06T10:05:37.528Z</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>card_1788689218236_4xl0ff</v>
+      </c>
+      <c r="B123" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+      <c r="C123" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D123" t="str">
+        <v>“How did you feel about the presentation?” and “What did you like best about the product?” are often asked in what data collection method?</v>
+      </c>
+      <c r="E123" t="str">
+        <v>Focus groups</v>
+      </c>
+      <c r="F123" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G123" t="str">
+        <v>2026-09-06T10:06:58.236Z</v>
+      </c>
+      <c r="H123" t="str">
+        <v>2026-09-06T10:06:58.236Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H122"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H123"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E212"/>
+  <dimension ref="A1:E213"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8846,9 +8872,26 @@
         <v>MAT110 - Lesson1</v>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>2026-09-06T18:06:58+08:00</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C213" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D213" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E213" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E212"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E213"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H123"/>
+  <dimension ref="A1:H124"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5291,16 +5291,42 @@
         <v>2026-09-06T10:06:58.236Z</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>card_1788689307143_y9icmi</v>
+      </c>
+      <c r="B124" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+      <c r="C124" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D124" t="str">
+        <v>These are used to ask questions that have closed-ended answers.</v>
+      </c>
+      <c r="E124" t="str">
+        <v>Questionnaires and surveys</v>
+      </c>
+      <c r="F124" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G124" t="str">
+        <v>2026-09-06T10:08:27.143Z</v>
+      </c>
+      <c r="H124" t="str">
+        <v>2026-09-06T10:08:27.143Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H123"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H124"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E213"/>
+  <dimension ref="A1:E214"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8889,9 +8915,26 @@
         <v>MAT110 - Lesson1</v>
       </c>
     </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>2026-09-06T18:08:27+08:00</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C214" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D214" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E214" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E213"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E214"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:H125"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5317,16 +5317,42 @@
         <v>2026-09-06T10:08:27.143Z</v>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>card_1788689355788_kcf2ek</v>
+      </c>
+      <c r="B125" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+      <c r="C125" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D125" t="str">
+        <v>It refers to the process of controlling as many factors as possible to isolate the effects of a particular factor.</v>
+      </c>
+      <c r="E125" t="str">
+        <v>Experimentation</v>
+      </c>
+      <c r="F125" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G125" t="str">
+        <v>2026-09-06T10:09:15.788Z</v>
+      </c>
+      <c r="H125" t="str">
+        <v>2026-09-06T10:09:15.788Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H124"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H125"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E214"/>
+  <dimension ref="A1:E215"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8932,9 +8958,26 @@
         <v>MAT110 - Lesson1</v>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>2026-09-06T18:09:15+08:00</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C215" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D215" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E215" t="str">
+        <v>MAT110 - Lesson1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E214"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E215"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H126"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5343,16 +5343,42 @@
         <v>2026-09-06T10:09:15.788Z</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>card_1788689638669_mq5lcz</v>
+      </c>
+      <c r="B126" t="str">
+        <v>MAT110 - Lesson2</v>
+      </c>
+      <c r="C126" t="str">
+        <v>cloze</v>
+      </c>
+      <c r="D126" t="str">
+        <v>A _____ is one that is not influenced by extremely high or low data values. The mean is not a _______ of center because we can make the mean as large as we want by changing the size of only one data value. The median, on the other hand, is more resistant. However, a disadvantage of the median is that it is not sensitive to the specific size of a data value.</v>
+      </c>
+      <c r="E126" t="str">
+        <v>resistant measure</v>
+      </c>
+      <c r="F126" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G126" t="str">
+        <v>2026-09-06T10:13:58.669Z</v>
+      </c>
+      <c r="H126" t="str">
+        <v>2026-09-06T10:13:58.669Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H125"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H126"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E215"/>
+  <dimension ref="A1:E216"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8975,9 +9001,26 @@
         <v>MAT110 - Lesson1</v>
       </c>
     </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>2026-09-06T18:13:58+08:00</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C216" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D216" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E216" t="str">
+        <v>MAT110 - Lesson2 — cloze</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E215"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E216"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H126"/>
+  <dimension ref="A1:H127"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5369,16 +5369,42 @@
         <v>2026-09-06T10:13:58.669Z</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>card_1788689668107_0e46be</v>
+      </c>
+      <c r="B127" t="str">
+        <v>MAT110 - Lesson2</v>
+      </c>
+      <c r="C127" t="str">
+        <v>cloze</v>
+      </c>
+      <c r="D127" t="str">
+        <v>A _____ is the mean of the data values left after trimming a specified percentage of the smallest and largest data values from the data set.</v>
+      </c>
+      <c r="E127" t="str">
+        <v>trimmed mean</v>
+      </c>
+      <c r="F127" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G127" t="str">
+        <v>2026-09-06T10:14:28.107Z</v>
+      </c>
+      <c r="H127" t="str">
+        <v>2026-09-06T10:14:28.107Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H126"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H127"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E216"/>
+  <dimension ref="A1:E217"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9018,9 +9044,26 @@
         <v>MAT110 - Lesson2 — cloze</v>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>2026-09-06T18:14:28+08:00</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C217" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D217" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E217" t="str">
+        <v>MAT110 - Lesson2 — cloze</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E216"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E217"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H128"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5395,16 +5395,42 @@
         <v>2026-09-06T10:14:28.107Z</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>card_1788690989883_l7rumg</v>
+      </c>
+      <c r="B128" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C128" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D128" t="str">
+        <v>This is the ultimate source of power and authority in an organization, overseeing its goals, policies, and procedures — consisting of the board of directors and the chief executive or managing director.</v>
+      </c>
+      <c r="E128" t="str">
+        <v>Administrative, Managerial, or Top Level of Management</v>
+      </c>
+      <c r="F128" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G128" t="str">
+        <v>2026-09-06T10:36:29.883Z</v>
+      </c>
+      <c r="H128" t="str">
+        <v>2026-09-06T10:36:29.883Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H127"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H128"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E217"/>
+  <dimension ref="A1:E218"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9061,9 +9087,26 @@
         <v>MAT110 - Lesson2 — cloze</v>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>2026-09-06T18:36:29+08:00</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C218" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D218" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E218" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E217"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E218"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:H129"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5421,16 +5421,42 @@
         <v>2026-09-06T10:36:29.883Z</v>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>card_1788691008066_umuuj6</v>
+      </c>
+      <c r="B129" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C129" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D129" t="str">
+        <v>This management level consists of the branch and departmental managers.</v>
+      </c>
+      <c r="E129" t="str">
+        <v>Executive or Middle Level of Management</v>
+      </c>
+      <c r="F129" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G129" t="str">
+        <v>2026-09-06T10:36:48.066Z</v>
+      </c>
+      <c r="H129" t="str">
+        <v>2026-09-06T10:36:48.066Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H128"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E218"/>
+  <dimension ref="A1:E219"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9104,9 +9130,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>2026-09-06T18:36:48+08:00</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C219" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D219" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E219" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E218"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E219"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H129"/>
+  <dimension ref="A1:H130"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5447,16 +5447,42 @@
         <v>2026-09-06T10:36:48.066Z</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>card_1788691020321_888htp</v>
+      </c>
+      <c r="B130" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C130" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D130" t="str">
+        <v>This management level consists of supervisors, foremen, section officers, and superintendents, primarily concerned with the execution and coordination of day-to-day workflow.</v>
+      </c>
+      <c r="E130" t="str">
+        <v>Supervisory, Operative, or Lower Level of Management</v>
+      </c>
+      <c r="F130" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G130" t="str">
+        <v>2026-09-06T10:37:00.321Z</v>
+      </c>
+      <c r="H130" t="str">
+        <v>2026-09-06T10:37:00.321Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H130"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E219"/>
+  <dimension ref="A1:E220"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9147,9 +9173,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>2026-09-06T18:37:00+08:00</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C220" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D220" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E220" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E219"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E220"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:H131"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5473,16 +5473,42 @@
         <v>2026-09-06T10:37:00.321Z</v>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>card_1788691036192_jwtrzy</v>
+      </c>
+      <c r="B131" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C131" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D131" t="str">
+        <v>This is the specific kind of enterprise system designed to integrate data across, and be comprehensive in supporting, all of an organization's major functions.</v>
+      </c>
+      <c r="E131" t="str">
+        <v>Enterprise Resource Planning (ERP) system</v>
+      </c>
+      <c r="F131" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G131" t="str">
+        <v>2026-09-06T10:37:16.192Z</v>
+      </c>
+      <c r="H131" t="str">
+        <v>2026-09-06T10:37:16.192Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H131"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E220"/>
+  <dimension ref="A1:E221"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9190,9 +9216,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>2026-09-06T18:37:16+08:00</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C221" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D221" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E221" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E220"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E221"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H131"/>
+  <dimension ref="A1:H132"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5499,16 +5499,42 @@
         <v>2026-09-06T10:37:16.192Z</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>card_1788691076030_487lha</v>
+      </c>
+      <c r="B132" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C132" t="str">
+        <v>cloze</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Outsourcing overseas, ethical issues, and problems with system security fall under Global, Ethical and _____.</v>
+      </c>
+      <c r="E132" t="str">
+        <v>Security Management</v>
+      </c>
+      <c r="F132" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G132" t="str">
+        <v>2026-09-06T10:37:56.030Z</v>
+      </c>
+      <c r="H132" t="str">
+        <v>2026-09-06T10:37:56.030Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H131"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H132"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E221"/>
+  <dimension ref="A1:E222"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9233,9 +9259,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>2026-09-06T18:37:56+08:00</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C222" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D222" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E222" t="str">
+        <v>ADV01 - Intro to EntSys n Mang. — cloze</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E221"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E222"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:H133"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5525,16 +5525,42 @@
         <v>2026-09-06T10:37:56.030Z</v>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>card_1788691099797_nf81jw</v>
+      </c>
+      <c r="B133" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C133" t="str">
+        <v>cloze</v>
+      </c>
+      <c r="D133" t="str">
+        <v>_____ helps prepare for changes to how business is done; communicating, preparing, and setting expectations is as important as providing training and support.</v>
+      </c>
+      <c r="E133" t="str">
+        <v>Change Management</v>
+      </c>
+      <c r="F133" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G133" t="str">
+        <v>2026-09-06T10:38:19.797Z</v>
+      </c>
+      <c r="H133" t="str">
+        <v>2026-09-06T10:38:19.797Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H132"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H133"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E222"/>
+  <dimension ref="A1:E223"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9276,9 +9302,26 @@
         <v>ADV01 - Intro to EntSys n Mang. — cloze</v>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>2026-09-06T18:38:19+08:00</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C223" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D223" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E223" t="str">
+        <v>ADV01 - Intro to EntSys n Mang. — cloze</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E222"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E223"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H134"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5551,16 +5551,42 @@
         <v>2026-09-06T10:38:19.797Z</v>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>card_1788691143290_lnzs0x</v>
+      </c>
+      <c r="B134" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C134" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D134" t="str">
+        <v>This term focuses on linking a business with its external partners and stakeholders, and was a disruptive technology that transformed buying, selling, customer service, and supplier relationships.</v>
+      </c>
+      <c r="E134" t="str">
+        <v>E-Business</v>
+      </c>
+      <c r="F134" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G134" t="str">
+        <v>2026-09-06T10:39:03.290Z</v>
+      </c>
+      <c r="H134" t="str">
+        <v>2026-09-06T10:39:03.290Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H133"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H134"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E223"/>
+  <dimension ref="A1:E224"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9319,9 +9345,26 @@
         <v>ADV01 - Intro to EntSys n Mang. — cloze</v>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>2026-09-06T18:39:03+08:00</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C224" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D224" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E224" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E223"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E224"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H134"/>
+  <dimension ref="A1:H135"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5577,16 +5577,42 @@
         <v>2026-09-06T10:39:03.290Z</v>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>card_1788691156362_wa1c4s</v>
+      </c>
+      <c r="B135" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C135" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D135" t="str">
+        <v>This term focuses on integrating the internal functional silos of an organization into an enterprise application, and was an adaptive technology merging early data processing and integration efforts.</v>
+      </c>
+      <c r="E135" t="str">
+        <v>ERP (Enterprise Resource Planning)</v>
+      </c>
+      <c r="F135" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G135" t="str">
+        <v>2026-09-06T10:39:16.362Z</v>
+      </c>
+      <c r="H135" t="str">
+        <v>2026-09-06T10:39:16.362Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H134"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H135"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E224"/>
+  <dimension ref="A1:E225"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9362,9 +9388,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>2026-09-06T18:39:16+08:00</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C225" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D225" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E225" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E224"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E225"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H136"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5603,16 +5603,42 @@
         <v>2026-09-06T10:39:16.362Z</v>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>card_1788691173665_q88m8j</v>
+      </c>
+      <c r="B136" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C136" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D136" t="str">
+        <v>This is the understanding, visibility, and control of business processes, following a prescribed methodology to help document and understand their use throughout the business.</v>
+      </c>
+      <c r="E136" t="str">
+        <v>Business Process Management (BPM)</v>
+      </c>
+      <c r="F136" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G136" t="str">
+        <v>2026-09-06T10:39:33.665Z</v>
+      </c>
+      <c r="H136" t="str">
+        <v>2026-09-06T10:39:33.665Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H135"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H136"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E225"/>
+  <dimension ref="A1:E226"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9405,9 +9431,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>2026-09-06T18:39:33+08:00</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C226" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D226" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E226" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E225"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E226"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H137"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5629,16 +5629,46 @@
         <v>2026-09-06T10:39:33.665Z</v>
       </c>
     </row>
+    <row r="137" xml:space="preserve">
+      <c r="A137" t="str">
+        <v>card_1788691240125_ktnige</v>
+      </c>
+      <c r="B137" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C137" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D137" t="str">
+        <v>Five(5) phases of the ERP Implementation Methodology</v>
+      </c>
+      <c r="E137" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Requirements Gathering/Gap Analysis,
+2. General System Design,
+3. Build and Test,
+4. Implementation,
+5. Stabilization and Production Support</v>
+      </c>
+      <c r="F137" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G137" t="str">
+        <v>2026-09-06T10:40:40.125Z</v>
+      </c>
+      <c r="H137" t="str">
+        <v>2026-09-06T10:40:40.125Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H136"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H137"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E226"/>
+  <dimension ref="A1:E227"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9448,9 +9478,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>2026-09-06T18:40:40+08:00</v>
+      </c>
+      <c r="B227" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C227" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D227" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E227" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E226"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E227"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H138"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5659,16 +5659,44 @@
         <v>2026-09-06T10:40:40.125Z</v>
       </c>
     </row>
+    <row r="138" xml:space="preserve">
+      <c r="A138" t="str">
+        <v>card_1788691281723_zpa0jt</v>
+      </c>
+      <c r="B138" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C138" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D138" t="str">
+        <v>Name the three tracks that run underneath all phases of the ERP Implementation Methodology</v>
+      </c>
+      <c r="E138" t="str" xml:space="preserve">
+        <v xml:space="preserve">Functional,
+Technical, and
+Change Management</v>
+      </c>
+      <c r="F138" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G138" t="str">
+        <v>2026-09-06T10:41:21.723Z</v>
+      </c>
+      <c r="H138" t="str">
+        <v>2026-09-06T10:41:21.723Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H137"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H138"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E227"/>
+  <dimension ref="A1:E228"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9495,9 +9523,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>2026-09-06T18:41:21+08:00</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C228" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D228" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E228" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E227"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E228"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H138"/>
+  <dimension ref="A1:H139"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5687,16 +5687,42 @@
         <v>2026-09-06T10:41:21.723Z</v>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>card_1788691301090_3lkzvu</v>
+      </c>
+      <c r="B139" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C139" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D139" t="str">
+        <v>This is one of the most critical points in a project's success — when the system starts being used in production.</v>
+      </c>
+      <c r="E139" t="str">
+        <v>Going live ("Go-live")</v>
+      </c>
+      <c r="F139" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G139" t="str">
+        <v>2026-09-06T10:41:41.090Z</v>
+      </c>
+      <c r="H139" t="str">
+        <v>2026-09-06T10:41:41.090Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H138"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H139"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E228"/>
+  <dimension ref="A1:E229"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9540,9 +9566,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>2026-09-06T18:41:41+08:00</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C229" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D229" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E229" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E228"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E229"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H140"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5713,16 +5713,42 @@
         <v>2026-09-06T10:41:41.090Z</v>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>card_1788691328072_zk3tzd</v>
+      </c>
+      <c r="B140" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C140" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D140" t="str">
+        <v>Name the three components of the Project Management Pyramid</v>
+      </c>
+      <c r="E140" t="str">
+        <v>Resources, Time, and Scope</v>
+      </c>
+      <c r="F140" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G140" t="str">
+        <v>2026-09-06T10:42:08.072Z</v>
+      </c>
+      <c r="H140" t="str">
+        <v>2026-09-06T10:42:08.072Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H139"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H140"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E229"/>
+  <dimension ref="A1:E230"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9583,9 +9609,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>2026-09-06T18:42:08+08:00</v>
+      </c>
+      <c r="B230" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C230" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D230" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E230" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E229"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E230"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H141"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5739,16 +5739,42 @@
         <v>2026-09-06T10:42:08.072Z</v>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>card_1788691348423_qe5z0w</v>
+      </c>
+      <c r="B141" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C141" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D141" t="str">
+        <v>Organizations without much ERP implementation experience often use these implementation partners.</v>
+      </c>
+      <c r="E141" t="str">
+        <v>Consultants</v>
+      </c>
+      <c r="F141" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G141" t="str">
+        <v>2026-09-06T10:42:28.423Z</v>
+      </c>
+      <c r="H141" t="str">
+        <v>2026-09-06T10:42:28.423Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H140"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H141"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E230"/>
+  <dimension ref="A1:E231"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9626,9 +9652,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>2026-09-06T18:42:28+08:00</v>
+      </c>
+      <c r="B231" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C231" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D231" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E231" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E230"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E231"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:H142"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5765,16 +5765,42 @@
         <v>2026-09-06T10:42:28.423Z</v>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>card_1788691361310_u0b8e2</v>
+      </c>
+      <c r="B142" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C142" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D142" t="str">
+        <v>This process involves changing, adjusting, or adapting business processes to fully use the functionality of an ERP system.</v>
+      </c>
+      <c r="E142" t="str">
+        <v>Business Process Re-engineering (BPR)</v>
+      </c>
+      <c r="F142" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G142" t="str">
+        <v>2026-09-06T10:42:41.310Z</v>
+      </c>
+      <c r="H142" t="str">
+        <v>2026-09-06T10:42:41.310Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H141"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H142"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E231"/>
+  <dimension ref="A1:E232"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9669,9 +9695,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>2026-09-06T18:42:41+08:00</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C232" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D232" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E232" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E231"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E232"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H142"/>
+  <dimension ref="A1:H143"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5791,16 +5791,42 @@
         <v>2026-09-06T10:42:41.310Z</v>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>card_1788691392741_jw28lt</v>
+      </c>
+      <c r="B143" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C143" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D143" t="str">
+        <v>This ERP vendor is recognized as the global leader among ERP vendors, with over 12 million users</v>
+      </c>
+      <c r="E143" t="str">
+        <v>SAP</v>
+      </c>
+      <c r="F143" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G143" t="str">
+        <v>2026-09-06T10:43:12.741Z</v>
+      </c>
+      <c r="H143" t="str">
+        <v>2026-09-06T10:43:12.741Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H142"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H143"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E232"/>
+  <dimension ref="A1:E233"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9712,9 +9738,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>2026-09-06T18:43:12+08:00</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C233" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D233" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E233" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E232"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E233"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H143"/>
+  <dimension ref="A1:H144"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5817,16 +5817,42 @@
         <v>2026-09-06T10:43:12.741Z</v>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>card_1788691408876_k0lf5q</v>
+      </c>
+      <c r="B144" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C144" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D144" t="str">
+        <v>This is the second largest ERP vendor, providing solutions by industry category and promising long-term support for PeopleSoft customers (acquired in 2004).</v>
+      </c>
+      <c r="E144" t="str">
+        <v>Oracle/PeopleSoft</v>
+      </c>
+      <c r="F144" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G144" t="str">
+        <v>2026-09-06T10:43:28.876Z</v>
+      </c>
+      <c r="H144" t="str">
+        <v>2026-09-06T10:43:28.876Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H143"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H144"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E233"/>
+  <dimension ref="A1:E234"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9755,9 +9781,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>2026-09-06T18:43:28+08:00</v>
+      </c>
+      <c r="B234" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C234" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D234" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E234" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E233"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E234"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H145"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5843,16 +5843,42 @@
         <v>2026-09-06T10:43:28.876Z</v>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>card_1788691420451_l99owz</v>
+      </c>
+      <c r="B145" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C145" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D145" t="str">
+        <v>This is the world's third largest provider of enterprise software, delivering integrated solutions in supply chain, customer relationship, and supplier management.</v>
+      </c>
+      <c r="E145" t="str">
+        <v>Infor</v>
+      </c>
+      <c r="F145" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G145" t="str">
+        <v>2026-09-06T10:43:40.451Z</v>
+      </c>
+      <c r="H145" t="str">
+        <v>2026-09-06T10:43:40.451Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H144"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H145"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E234"/>
+  <dimension ref="A1:E235"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9798,9 +9824,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>2026-09-06T18:43:40+08:00</v>
+      </c>
+      <c r="B235" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C235" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D235" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E235" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E234"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E235"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H146"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5869,16 +5869,42 @@
         <v>2026-09-06T10:43:40.451Z</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>card_1788691432267_y3ggzb</v>
+      </c>
+      <c r="B146" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C146" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D146" t="str">
+        <v>This vendor, formerly known as Microsoft Business Solutions or Great Plains, is a comprehensive business-management solution built on the Microsoft platform.</v>
+      </c>
+      <c r="E146" t="str">
+        <v>Microsoft Dynamics</v>
+      </c>
+      <c r="F146" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G146" t="str">
+        <v>2026-09-06T10:43:52.267Z</v>
+      </c>
+      <c r="H146" t="str">
+        <v>2026-09-06T10:43:52.267Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H145"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H146"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E235"/>
+  <dimension ref="A1:E236"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9841,9 +9867,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>2026-09-06T18:43:52+08:00</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C236" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D236" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E236" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E235"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E236"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:H147"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5895,16 +5895,42 @@
         <v>2026-09-06T10:43:52.267Z</v>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>card_1788691446674_utb3m6</v>
+      </c>
+      <c r="B147" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C147" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D147" t="str">
+        <v>This ERP vendor acquired Baan in 2004 and claims to offer solutions that accomplish specific goals in shorter time frames.</v>
+      </c>
+      <c r="E147" t="str">
+        <v>SSA Global</v>
+      </c>
+      <c r="F147" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G147" t="str">
+        <v>2026-09-06T10:44:06.674Z</v>
+      </c>
+      <c r="H147" t="str">
+        <v>2026-09-06T10:44:06.674Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H146"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H147"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E236"/>
+  <dimension ref="A1:E237"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9884,9 +9910,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>2026-09-06T18:44:06+08:00</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C237" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D237" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E237" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E236"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E237"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H147"/>
+  <dimension ref="A1:H148"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5921,16 +5921,42 @@
         <v>2026-09-06T10:44:06.674Z</v>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>card_1788691461465_twzth0</v>
+      </c>
+      <c r="B148" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C148" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D148" t="str">
+        <v>Name the three ERP market tiers into which vendors are classified.</v>
+      </c>
+      <c r="E148" t="str">
+        <v>Tier I, Tier II, and Tier III</v>
+      </c>
+      <c r="F148" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G148" t="str">
+        <v>2026-09-06T10:44:21.465Z</v>
+      </c>
+      <c r="H148" t="str">
+        <v>2026-09-06T10:44:21.465Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H147"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H148"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E237"/>
+  <dimension ref="A1:E238"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9927,9 +9953,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>2026-09-06T18:44:21+08:00</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C238" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D238" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E238" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E237"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E238"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H148"/>
+  <dimension ref="A1:H149"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5947,16 +5947,42 @@
         <v>2026-09-06T10:44:21.465Z</v>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>card_1788691505967_hixupa</v>
+      </c>
+      <c r="B149" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C149" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D149" t="str">
+        <v>In the 1960s, ERP evolution focused on this type of system, run on mainframe legacy platforms using third-generation software such as Cobol and Fortran.</v>
+      </c>
+      <c r="E149" t="str">
+        <v>Inventory management and control</v>
+      </c>
+      <c r="F149" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G149" t="str">
+        <v>2026-09-06T10:45:05.966Z</v>
+      </c>
+      <c r="H149" t="str">
+        <v>2026-09-06T10:45:05.966Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H148"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H149"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E238"/>
+  <dimension ref="A1:E239"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -9970,9 +9996,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>2026-09-06T18:45:05+08:00</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C239" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D239" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E239" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E238"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E239"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H149"/>
+  <dimension ref="A1:H150"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5973,16 +5973,42 @@
         <v>2026-09-06T10:45:05.966Z</v>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>card_1788691521822_nc1e3p</v>
+      </c>
+      <c r="B150" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C150" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D150" t="str">
+        <v>In the 1970s, this system focused on sales and marketing and was designed for job shop scheduling.</v>
+      </c>
+      <c r="E150" t="str">
+        <v>Material Requirements Planning (MRP)</v>
+      </c>
+      <c r="F150" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G150" t="str">
+        <v>2026-09-06T10:45:21.822Z</v>
+      </c>
+      <c r="H150" t="str">
+        <v>2026-09-06T10:45:21.822Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H149"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H150"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E239"/>
+  <dimension ref="A1:E240"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -10013,9 +10039,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>2026-09-06T18:45:21+08:00</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C240" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D240" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E240" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E239"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E240"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H151"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -5999,16 +5999,42 @@
         <v>2026-09-06T10:45:21.822Z</v>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>card_1788691536957_w09k2t</v>
+      </c>
+      <c r="B151" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C151" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D151" t="str">
+        <v>In the 1980s, this system focused on manufacturing strategy and quality control, helping production managers design production supply chain processes.</v>
+      </c>
+      <c r="E151" t="str">
+        <v>Manufacturing Requirements Planning (MRP II)</v>
+      </c>
+      <c r="F151" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G151" t="str">
+        <v>2026-09-06T10:45:36.957Z</v>
+      </c>
+      <c r="H151" t="str">
+        <v>2026-09-06T10:45:36.957Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H150"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H151"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E240"/>
+  <dimension ref="A1:E241"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -10056,9 +10082,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>2026-09-06T18:45:36+08:00</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C241" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D241" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E241" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E240"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E241"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H152"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -6025,16 +6025,42 @@
         <v>2026-09-06T10:45:36.957Z</v>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>card_1788691549460_7pvd88</v>
+      </c>
+      <c r="B152" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C152" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D152" t="str">
+        <v>In the 2000s, this extended the first-generation ERP with a focus on agility and a customer-centric global environment, integrating with SCM, CRM, and SFA applications.</v>
+      </c>
+      <c r="E152" t="str">
+        <v>Extended ERP or ERP II</v>
+      </c>
+      <c r="F152" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G152" t="str">
+        <v>2026-09-06T10:45:49.460Z</v>
+      </c>
+      <c r="H152" t="str">
+        <v>2026-09-06T10:45:49.460Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H151"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H152"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E241"/>
+  <dimension ref="A1:E242"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -10099,9 +10125,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>2026-09-06T18:45:49+08:00</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C242" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D242" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E242" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E241"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E242"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H153"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -6051,16 +6051,42 @@
         <v>2026-09-06T10:45:49.460Z</v>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>card_1788691563803_i1lgut</v>
+      </c>
+      <c r="B153" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C153" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D153" t="str">
+        <v>These are the five components an ERP system depends on to perform the input, process, and output phases of a system.</v>
+      </c>
+      <c r="E153" t="str">
+        <v>Hardware, Software, Information, Process, and People</v>
+      </c>
+      <c r="F153" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G153" t="str">
+        <v>2026-09-06T10:46:03.803Z</v>
+      </c>
+      <c r="H153" t="str">
+        <v>2026-09-06T10:46:03.803Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H152"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H153"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E242"/>
+  <dimension ref="A1:E243"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -10142,9 +10168,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>2026-09-06T18:46:03+08:00</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C243" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D243" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E243" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E242"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E243"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:H154"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -6077,16 +6077,42 @@
         <v>2026-09-06T10:46:03.803Z</v>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>card_1788691582651_09kywe</v>
+      </c>
+      <c r="B154" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C154" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D154" t="str">
+        <v>This is a blueprint of the actual ERP system that transforms the high-level ERP implementation strategy into an information flow with interrelationships in the organization.</v>
+      </c>
+      <c r="E154" t="str">
+        <v>System (ERP) architecture</v>
+      </c>
+      <c r="F154" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G154" t="str">
+        <v>2026-09-06T10:46:22.651Z</v>
+      </c>
+      <c r="H154" t="str">
+        <v>2026-09-06T10:46:22.651Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H153"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H154"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E243"/>
+  <dimension ref="A1:E244"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -10185,9 +10211,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>2026-09-06T18:46:22+08:00</v>
+      </c>
+      <c r="B244" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C244" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D244" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E244" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E243"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E244"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H154"/>
+  <dimension ref="A1:H155"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -6103,16 +6103,42 @@
         <v>2026-09-06T10:46:22.651Z</v>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>card_1788691598561_vjnfiz</v>
+      </c>
+      <c r="B155" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C155" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D155" t="str">
+        <v>This type of ERP architecture focuses on supporting the requirements of the end-users.</v>
+      </c>
+      <c r="E155" t="str">
+        <v>Logical architecture</v>
+      </c>
+      <c r="F155" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G155" t="str">
+        <v>2026-09-06T10:46:38.561Z</v>
+      </c>
+      <c r="H155" t="str">
+        <v>2026-09-06T10:46:38.561Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H154"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H155"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E244"/>
+  <dimension ref="A1:E245"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -10228,9 +10254,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>2026-09-06T18:46:38+08:00</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C245" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D245" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E245" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E244"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E245"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:H156"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -6129,16 +6129,42 @@
         <v>2026-09-06T10:46:38.561Z</v>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>card_1788691611873_eau9nc</v>
+      </c>
+      <c r="B156" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C156" t="str">
+        <v>basic</v>
+      </c>
+      <c r="D156" t="str">
+        <v>This type of ERP architecture focuses on the efficiency (cost, response time, etc.) of the system.</v>
+      </c>
+      <c r="E156" t="str">
+        <v>Physical architecture</v>
+      </c>
+      <c r="F156" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G156" t="str">
+        <v>2026-09-06T10:46:51.873Z</v>
+      </c>
+      <c r="H156" t="str">
+        <v>2026-09-06T10:46:51.873Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H155"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H156"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E245"/>
+  <dimension ref="A1:E246"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -10271,9 +10297,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>2026-09-06T18:46:51+08:00</v>
+      </c>
+      <c r="B246" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C246" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D246" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E246" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E245"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E246"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Subject_Scheduler.xlsx
+++ b/Subject_Scheduler.xlsx
@@ -2139,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H156"/>
+  <dimension ref="A1:H157"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -6155,16 +6155,42 @@
         <v>2026-09-06T10:46:51.873Z</v>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>card_1788691649127_l6q6vz</v>
+      </c>
+      <c r="B157" t="str">
+        <v>ADV01 - Intro to EntSys n Mang.</v>
+      </c>
+      <c r="C157" t="str">
+        <v>cloze</v>
+      </c>
+      <c r="D157" t="str">
+        <v>ERP acts as a _____, eliminating data redundancy and adding flexibility.</v>
+      </c>
+      <c r="E157" t="str">
+        <v>central repository</v>
+      </c>
+      <c r="F157" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="G157" t="str">
+        <v>2026-09-06T10:47:29.127Z</v>
+      </c>
+      <c r="H157" t="str">
+        <v>2026-09-06T10:47:29.127Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H156"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H157"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E246"/>
+  <dimension ref="A1:E247"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -10314,9 +10340,26 @@
         <v>ADV01 - Intro to EntSys n Mang.</v>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>2026-09-06T18:47:29+08:00</v>
+      </c>
+      <c r="B247" t="str">
+        <v>Bert</v>
+      </c>
+      <c r="C247" t="str">
+        <v>Master</v>
+      </c>
+      <c r="D247" t="str">
+        <v>Add Flashcard</v>
+      </c>
+      <c r="E247" t="str">
+        <v>ADV01 - Intro to EntSys n Mang. — cloze</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E246"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E247"/>
   </ignoredErrors>
 </worksheet>
 </file>
